--- a/content/RK-World-LinkedIn-Content-Plan.xlsx
+++ b/content/RK-World-LinkedIn-Content-Plan.xlsx
@@ -1944,10 +1944,10 @@
         <v/>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>Weekly cadence</t>
+    <row r="12" ht="26" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Column F is a live COUNTIF against the Content Calendar tab, so it updates when you add or rename posts. Expected values: 3 / 2 / 3 / 2 / 2 / 2, total 14. Excel computes these on open; they may appear blank in a non-Excel previewer until then.</t>
         </is>
       </c>
     </row>
@@ -2045,8 +2045,9 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A12:F12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/content/RK-World-LinkedIn-Content-Plan.xlsx
+++ b/content/RK-World-LinkedIn-Content-Plan.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Sources" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Content Calendar'!$A$4:$I$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Content Calendar'!$A$4:$I$19</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -501,7 +501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1206,15 +1206,63 @@
         </is>
       </c>
     </row>
+    <row r="19" ht="46" customHeight="1">
+      <c r="A19" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Category &amp; market POV</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>Listed everywhere vs available everywhere</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>Your brand is listed everywhere. But is it available everywhere?</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>Opinion / 3-point breakdown</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>Reach + inbound from brand teams</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+    </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" s="2" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>Yellow = quotes financial figures sourced from third-party records; confirm internally before publishing.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:I18"/>
+  <autoFilter ref="A4:I19"/>
   <mergeCells count="2">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:I2"/>
@@ -1229,7 +1277,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1692,6 +1740,44 @@
       <c r="E17" s="5" t="inlineStr">
         <is>
           <t>#Milestone #Growth #Ecommerce #FMCG</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="338" customHeight="1">
+      <c r="A18" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Category &amp; market POV</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Listed everywhere vs available everywhere</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>Your brand is listed everywhere.
+But is it available everywhere?
+Those aren't the same sentence. Most brands find that out the expensive way.
+A listing says your product exists. Availability says a customer in Siliguri can actually receive it - this week, at the price you set.
+Between those two facts sit three quiet failures:
+Listed, but out of stock. The page is live. The Buy Box isn't yours. A competitor's product just became the default answer to your brand name.
+Listed, but not serviceable. The customer finds you, enters their pin code, and the estimate reads seven days. They don't wait. They substitute.
+Listed, but in the wrong warehouse. Your inventory sits 1,800 km from the demand. Your ad spend created the intent. Someone else's supply chain captured it.
+None of these show up in a listing audit.
+All of them show up in your revenue.
+This is the whole reason we built the way we did - 125+ fulfilment centres, 19,000+ pin codes, 2,800+ brands.
+Not because scale is a vanity metric. Because available is a promise you can only keep by having inventory in the right place BEFORE the customer searches.
+Visibility gets you found.
+Availability gets you bought.</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>#Ecommerce #FMCG #SupplyChain #Retail #BrandStrategy</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1870,7 @@
         </is>
       </c>
       <c r="F4" s="7">
-        <f>COUNTIF('Content Calendar'!$B$5:$B$18,B4)</f>
+        <f>COUNTIF('Content Calendar'!$B$5:$B$19,B4)</f>
         <v/>
       </c>
     </row>
@@ -1813,7 +1899,7 @@
         </is>
       </c>
       <c r="F5" s="8">
-        <f>COUNTIF('Content Calendar'!$B$5:$B$18,B5)</f>
+        <f>COUNTIF('Content Calendar'!$B$5:$B$19,B5)</f>
         <v/>
       </c>
     </row>
@@ -1842,7 +1928,7 @@
         </is>
       </c>
       <c r="F6" s="7">
-        <f>COUNTIF('Content Calendar'!$B$5:$B$18,B6)</f>
+        <f>COUNTIF('Content Calendar'!$B$5:$B$19,B6)</f>
         <v/>
       </c>
     </row>
@@ -1871,7 +1957,7 @@
         </is>
       </c>
       <c r="F7" s="8">
-        <f>COUNTIF('Content Calendar'!$B$5:$B$18,B7)</f>
+        <f>COUNTIF('Content Calendar'!$B$5:$B$19,B7)</f>
         <v/>
       </c>
     </row>
@@ -1900,7 +1986,7 @@
         </is>
       </c>
       <c r="F8" s="7">
-        <f>COUNTIF('Content Calendar'!$B$5:$B$18,B8)</f>
+        <f>COUNTIF('Content Calendar'!$B$5:$B$19,B8)</f>
         <v/>
       </c>
     </row>
@@ -1929,7 +2015,7 @@
         </is>
       </c>
       <c r="F9" s="8">
-        <f>COUNTIF('Content Calendar'!$B$5:$B$18,B9)</f>
+        <f>COUNTIF('Content Calendar'!$B$5:$B$19,B9)</f>
         <v/>
       </c>
     </row>
@@ -1947,7 +2033,7 @@
     <row r="12" ht="26" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Column F is a live COUNTIF against the Content Calendar tab, so it updates when you add or rename posts. Expected values: 3 / 2 / 3 / 2 / 2 / 2, total 14. Excel computes these on open; they may appear blank in a non-Excel previewer until then.</t>
+          <t>Column F is a live COUNTIF against the Content Calendar tab, so it updates when you add or rename posts. Expected values: 3 / 2 / 4 / 2 / 2 / 2, total 15. Excel computes these on open; they may appear blank in a non-Excel previewer until then.</t>
         </is>
       </c>
     </row>
